--- a/vns-template.xlsx
+++ b/vns-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miri\Downloads\Kaetec\AIT\vns\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miri\git\genexcelbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF27E52-3EB0-4ABE-BB3D-633BD4902D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D38DBB-C274-48B6-8F12-42758122A679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="4290" windowWidth="32570" windowHeight="14800" xr2:uid="{320A5498-57DC-4B17-B13E-D4EC674CFE86}"/>
+    <workbookView xWindow="45972" yWindow="48" windowWidth="46296" windowHeight="25416" xr2:uid="{320A5498-57DC-4B17-B13E-D4EC674CFE86}"/>
   </bookViews>
   <sheets>
     <sheet name="2023xxxxxxxx-vns_確認" sheetId="9" r:id="rId1"/>
@@ -1332,7 +1332,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="45">
     <dxf>
       <fill>
         <patternFill>
@@ -1392,6 +1392,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -1399,6 +1406,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -1427,6 +1448,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -1456,6 +1484,167 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1805,6 +1994,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_LABS_GENERATIVEAI</we:customFunctionIds>
@@ -3200,64 +3392,49 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A29:M29 A2:M23">
-    <cfRule type="expression" dxfId="17" priority="31">
+  <conditionalFormatting sqref="A2:M23 A29:M29">
+    <cfRule type="expression" dxfId="28" priority="33">
+      <formula>$K2="更新版適用済"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="34">
       <formula>$K2="修正版適用待ち"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="32">
+    <cfRule type="expression" dxfId="26" priority="35" stopIfTrue="1">
       <formula>$K2="修正版配布待ち"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="33">
-      <formula>$K2="更新版適用済"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="34">
-      <formula>$K2="修正版適用待ち"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="35" stopIfTrue="1">
-      <formula>$K2="修正版配布待ち"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="36" stopIfTrue="1">
       <formula>$K2="更新版適用済"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:M29">
+    <cfRule type="expression" dxfId="24" priority="7" stopIfTrue="1">
+      <formula>$K2="修正版適用待ち"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="12" stopIfTrue="1">
+      <formula>$K2="更新版適用済"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="11" stopIfTrue="1">
+      <formula>$K2="修正版配布待ち"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="expression" dxfId="11" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>$K30="修正版適用待ち"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$K30="修正版配布待ち"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>$K30="更新版適用済"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="22">
+    <cfRule type="expression" dxfId="18" priority="22">
       <formula>$K30="修正版適用待ち"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="23" stopIfTrue="1">
       <formula>$K30="修正版配布待ち"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="24" stopIfTrue="1">
       <formula>$K30="更新版適用済"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24:M28">
-    <cfRule type="expression" dxfId="5" priority="7">
-      <formula>$K24="修正版適用待ち"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
-      <formula>$K24="修正版配布待ち"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="9">
-      <formula>$K24="更新版適用済"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="10">
-      <formula>$K24="修正版適用待ち"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
-      <formula>$K24="修正版配布待ち"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="12" stopIfTrue="1">
-      <formula>$K24="更新版適用済"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
